--- a/算法检测逻辑与参数总览.xlsx
+++ b/算法检测逻辑与参数总览.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8200" firstSheet="7" activeTab="8"/>
+    <workbookView windowWidth="18350" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="系统架构总览" sheetId="1" r:id="rId1"/>
@@ -953,7 +953,7 @@
     <t>P2:小样本偏离</t>
   </si>
   <si>
-    <t>50~100</t>
+    <t>50~100（偏离率绝对值×100）</t>
   </si>
   <si>
     <t>rule_p2_small_sample_deviation</t>
@@ -1169,11 +1169,30 @@
     <t>KDE详述</t>
   </si>
   <si>
-    <t>①按sku_name分组
+    <r>
+      <t>①按sku_name分组
 ②KDE拟合历史价格
 ③log_density（对数概率密度函数）排名转百分位
-④百分位≥95%分位数得分（分数即所在百分位值）
+④百分位≥95%分位数得分</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（分数即所在百分位值）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 ⑤价格偏离中位&lt;50%的不得分</t>
+    </r>
   </si>
   <si>
     <t/>
@@ -1200,11 +1219,30 @@
     <t>对样本量≥10且规则未命中(score&lt;70)的行</t>
   </si>
   <si>
-    <t>①按sku_name分组
+    <r>
+      <t>①按sku_name分组
 ②KDE拟合历史数量
 ③log_density（对数概率密度）排名转百分位
-④百分位≥95%得分
+④百分位≥95%得分</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（分数即所在百分位值）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 ⑤低于"max(10,均值×3)"的不得分</t>
+    </r>
   </si>
   <si>
     <t>qty_score = max(rule_score, ml_score) → 后过滤</t>
@@ -1496,7 +1534,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1669,6 +1707,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
